--- a/src/assets/downloads/LZK-Rechner_Pkw_V1.2.xlsx
+++ b/src/assets/downloads/LZK-Rechner_Pkw_V1.2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20406"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Basisprojekt/03_Arbeitsdokumente/AP4 Entwicklung Methodik und Umsetzung in Instrumenten/LZK-Rechner/Aktueller LZK-Rechner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0163F6E8-9788-44CD-B6AF-E54269FA8B27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{0163F6E8-9788-44CD-B6AF-E54269FA8B27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D262551F-AACA-4F57-9D33-E81BE5E5591E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1559,16 +1559,10 @@
     <t>https://nextmove.de/analyse-zum-deutschen-elektroauto-markt/</t>
   </si>
   <si>
-    <t>https://www.ifeu.de/projekt/analyse-der-umweltbilanz-von-kraftfahrzeugen-mit-alternativen-antrieben-oder-kraftstoffen-auf-dem-weg-zu-einem-treibhausgasneutralen-verkehr/</t>
-  </si>
-  <si>
     <t>TREMOD (2020)</t>
   </si>
   <si>
     <t>Transport Emission Model, ifeu</t>
-  </si>
-  <si>
-    <t>Methodenkonvention 3.1 zur Ermittlung von Umweltkosten</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.umweltbundesamt.de/sites/default/files/medien/1410/publikationen/2020-12-21_methodenkonvention_3_1_kostensaetze.pdf </t>
@@ -1662,9 +1656,6 @@
   </si>
   <si>
     <t>https://www.isi.fraunhofer.de/content/dam/isi/dokumente/cce/2021/BMU_Kurzpapier_UF_final.pdf</t>
-  </si>
-  <si>
-    <t>Realistic Test Cycle Assessment of Plug-in Hybrid Electric Vehicles in Europe</t>
   </si>
   <si>
     <t>Plötz &amp; Jöhrens (2021)</t>
@@ -2812,12 +2803,6 @@
     <t>Eigener Wert:</t>
   </si>
   <si>
-    <t>Biemann et al. (2023)</t>
-  </si>
-  <si>
-    <t>Analyse der Umweltbilanz von Kraftfahrzeugen mit alternativen Antrieben oder Kraftstoffen auf dem Weg zu einem treibhausgasneutralen Verkehr - ifeu-Projekt (laufend) für das UBA</t>
-  </si>
-  <si>
     <t>ADAC Preise für Erdgas (CNG)</t>
   </si>
   <si>
@@ -2887,6 +2872,21 @@
   </si>
   <si>
     <t>Version 1.2 - 10.01.2024</t>
+  </si>
+  <si>
+    <t>Biemann et al. (2024)</t>
+  </si>
+  <si>
+    <t>Methodenkonvention 3.1 zur Ermittlung von Umweltkosten - Kostensätze. Stand 12/2020. Umweltbundesamt.</t>
+  </si>
+  <si>
+    <t>Analyse der Umweltbilanz von Kraftfahrzeugen mit alternativen Antrieben oder Kraftstoffen auf dem Weg zu einem treibhausgasneutralen Verkehr. Umweltbundesamt.</t>
+  </si>
+  <si>
+    <t>https://www.umweltbundesamt.de/publikationen/analyse-der-umweltbilanz-von-kraftfahrzeugen</t>
+  </si>
+  <si>
+    <t>Realistic Test Cycle Assessment of Plug-in Hybrid Electric Vehicles in Europe. Fraunhofer ISI.</t>
   </si>
 </sst>
 </file>
@@ -4904,9 +4904,6 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4980,6 +4977,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
@@ -5017,15 +5023,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -5185,6 +5182,9 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -13160,7 +13160,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="16" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -13170,7 +13170,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="332" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -13192,17 +13192,17 @@
       <c r="J4" s="127"/>
     </row>
     <row r="5" spans="2:10" ht="124.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="369" t="s">
-        <v>480</v>
-      </c>
-      <c r="C5" s="369"/>
-      <c r="D5" s="369"/>
-      <c r="E5" s="369"/>
-      <c r="F5" s="369"/>
-      <c r="G5" s="369"/>
-      <c r="H5" s="369"/>
-      <c r="I5" s="369"/>
-      <c r="J5" s="369"/>
+      <c r="B5" s="371" t="s">
+        <v>477</v>
+      </c>
+      <c r="C5" s="371"/>
+      <c r="D5" s="371"/>
+      <c r="E5" s="371"/>
+      <c r="F5" s="371"/>
+      <c r="G5" s="371"/>
+      <c r="H5" s="371"/>
+      <c r="I5" s="371"/>
+      <c r="J5" s="371"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="330"/>
@@ -13240,13 +13240,13 @@
     <row r="9" spans="2:10" ht="50.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="293"/>
       <c r="E9" s="293"/>
-      <c r="F9" s="370" t="s">
+      <c r="F9" s="372" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="371"/>
-      <c r="H9" s="371"/>
-      <c r="I9" s="371"/>
-      <c r="J9" s="371"/>
+      <c r="G9" s="373"/>
+      <c r="H9" s="373"/>
+      <c r="I9" s="373"/>
+      <c r="J9" s="373"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="293"/>
@@ -13260,31 +13260,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="293"/>
       <c r="E11" s="293"/>
-      <c r="F11" s="372" t="s">
-        <v>196</v>
-      </c>
-      <c r="G11" s="373"/>
-      <c r="H11" s="373"/>
-      <c r="I11" s="373"/>
-      <c r="J11" s="373"/>
+      <c r="F11" s="374" t="s">
+        <v>194</v>
+      </c>
+      <c r="G11" s="375"/>
+      <c r="H11" s="375"/>
+      <c r="I11" s="375"/>
+      <c r="J11" s="375"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="293"/>
       <c r="E12" s="293"/>
-      <c r="F12" s="373"/>
-      <c r="G12" s="373"/>
-      <c r="H12" s="373"/>
-      <c r="I12" s="373"/>
-      <c r="J12" s="373"/>
+      <c r="F12" s="375"/>
+      <c r="G12" s="375"/>
+      <c r="H12" s="375"/>
+      <c r="I12" s="375"/>
+      <c r="J12" s="375"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="293"/>
       <c r="E13" s="293"/>
-      <c r="F13" s="373"/>
-      <c r="G13" s="373"/>
-      <c r="H13" s="373"/>
-      <c r="I13" s="373"/>
-      <c r="J13" s="373"/>
+      <c r="F13" s="375"/>
+      <c r="G13" s="375"/>
+      <c r="H13" s="375"/>
+      <c r="I13" s="375"/>
+      <c r="J13" s="375"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="293"/>
@@ -13298,22 +13298,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="293"/>
       <c r="E15" s="293"/>
-      <c r="F15" s="374" t="s">
-        <v>467</v>
-      </c>
-      <c r="G15" s="375"/>
-      <c r="H15" s="375"/>
-      <c r="I15" s="375"/>
-      <c r="J15" s="375"/>
+      <c r="F15" s="376" t="s">
+        <v>464</v>
+      </c>
+      <c r="G15" s="377"/>
+      <c r="H15" s="377"/>
+      <c r="I15" s="377"/>
+      <c r="J15" s="377"/>
     </row>
     <row r="16" spans="2:10" ht="73.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="293"/>
       <c r="E16" s="293"/>
-      <c r="F16" s="375"/>
-      <c r="G16" s="375"/>
-      <c r="H16" s="375"/>
-      <c r="I16" s="375"/>
-      <c r="J16" s="375"/>
+      <c r="F16" s="377"/>
+      <c r="G16" s="377"/>
+      <c r="H16" s="377"/>
+      <c r="I16" s="377"/>
+      <c r="J16" s="377"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="293"/>
@@ -13327,13 +13327,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="293"/>
       <c r="E18" s="293"/>
-      <c r="F18" s="376" t="s">
+      <c r="F18" s="378" t="s">
         <v>2</v>
       </c>
-      <c r="G18" s="377"/>
-      <c r="H18" s="377"/>
-      <c r="I18" s="377"/>
-      <c r="J18" s="377"/>
+      <c r="G18" s="379"/>
+      <c r="H18" s="379"/>
+      <c r="I18" s="379"/>
+      <c r="J18" s="379"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="293"/>
@@ -13347,31 +13347,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="293"/>
       <c r="E20" s="293"/>
-      <c r="F20" s="378" t="s">
+      <c r="F20" s="380" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="378"/>
-      <c r="H20" s="378"/>
-      <c r="I20" s="378"/>
-      <c r="J20" s="378"/>
+      <c r="G20" s="380"/>
+      <c r="H20" s="380"/>
+      <c r="I20" s="380"/>
+      <c r="J20" s="380"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="293"/>
       <c r="E21" s="293"/>
-      <c r="F21" s="378"/>
-      <c r="G21" s="378"/>
-      <c r="H21" s="378"/>
-      <c r="I21" s="378"/>
-      <c r="J21" s="378"/>
+      <c r="F21" s="380"/>
+      <c r="G21" s="380"/>
+      <c r="H21" s="380"/>
+      <c r="I21" s="380"/>
+      <c r="J21" s="380"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="293"/>
       <c r="E22" s="293"/>
-      <c r="F22" s="378"/>
-      <c r="G22" s="378"/>
-      <c r="H22" s="378"/>
-      <c r="I22" s="378"/>
-      <c r="J22" s="378"/>
+      <c r="F22" s="380"/>
+      <c r="G22" s="380"/>
+      <c r="H22" s="380"/>
+      <c r="I22" s="380"/>
+      <c r="J22" s="380"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="293"/>
@@ -13385,22 +13385,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="293"/>
       <c r="E24" s="293"/>
-      <c r="F24" s="379" t="s">
-        <v>466</v>
-      </c>
-      <c r="G24" s="379"/>
-      <c r="H24" s="379"/>
-      <c r="I24" s="379"/>
-      <c r="J24" s="379"/>
+      <c r="F24" s="381" t="s">
+        <v>463</v>
+      </c>
+      <c r="G24" s="381"/>
+      <c r="H24" s="381"/>
+      <c r="I24" s="381"/>
+      <c r="J24" s="381"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="293"/>
       <c r="E25" s="293"/>
-      <c r="F25" s="379"/>
-      <c r="G25" s="379"/>
-      <c r="H25" s="379"/>
-      <c r="I25" s="379"/>
-      <c r="J25" s="379"/>
+      <c r="F25" s="381"/>
+      <c r="G25" s="381"/>
+      <c r="H25" s="381"/>
+      <c r="I25" s="381"/>
+      <c r="J25" s="381"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="293"/>
@@ -13414,53 +13414,53 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="293"/>
       <c r="E27" s="293"/>
-      <c r="F27" s="368"/>
-      <c r="G27" s="368"/>
-      <c r="H27" s="368"/>
-      <c r="I27" s="368"/>
-      <c r="J27" s="368"/>
+      <c r="F27" s="370"/>
+      <c r="G27" s="370"/>
+      <c r="H27" s="370"/>
+      <c r="I27" s="370"/>
+      <c r="J27" s="370"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="293"/>
       <c r="E28" s="293"/>
-      <c r="F28" s="380" t="s">
+      <c r="F28" s="382" t="s">
         <v>4</v>
       </c>
-      <c r="G28" s="380"/>
-      <c r="H28" s="380"/>
-      <c r="I28" s="380"/>
-      <c r="J28" s="380"/>
+      <c r="G28" s="382"/>
+      <c r="H28" s="382"/>
+      <c r="I28" s="382"/>
+      <c r="J28" s="382"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="293"/>
       <c r="E29" s="293"/>
-      <c r="F29" s="380"/>
-      <c r="G29" s="380"/>
-      <c r="H29" s="380"/>
-      <c r="I29" s="380"/>
-      <c r="J29" s="380"/>
+      <c r="F29" s="382"/>
+      <c r="G29" s="382"/>
+      <c r="H29" s="382"/>
+      <c r="I29" s="382"/>
+      <c r="J29" s="382"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="293"/>
       <c r="E30" s="293"/>
-      <c r="F30" s="380"/>
-      <c r="G30" s="380"/>
-      <c r="H30" s="380"/>
-      <c r="I30" s="380"/>
-      <c r="J30" s="380"/>
+      <c r="F30" s="382"/>
+      <c r="G30" s="382"/>
+      <c r="H30" s="382"/>
+      <c r="I30" s="382"/>
+      <c r="J30" s="382"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="293"/>
       <c r="E31" s="293"/>
-      <c r="F31" s="381"/>
-      <c r="G31" s="381"/>
-      <c r="H31" s="381"/>
-      <c r="I31" s="381"/>
-      <c r="J31" s="381"/>
+      <c r="F31" s="369"/>
+      <c r="G31" s="369"/>
+      <c r="H31" s="369"/>
+      <c r="I31" s="369"/>
+      <c r="J31" s="369"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="308" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C32" s="309"/>
       <c r="D32" s="310"/>
@@ -13505,15 +13505,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="128"/>
       <c r="C36" s="125"/>
-      <c r="D36" s="381" t="s">
-        <v>195</v>
-      </c>
-      <c r="E36" s="381"/>
-      <c r="F36" s="381"/>
-      <c r="G36" s="381"/>
-      <c r="H36" s="381"/>
-      <c r="I36" s="381"/>
-      <c r="J36" s="381"/>
+      <c r="D36" s="369" t="s">
+        <v>193</v>
+      </c>
+      <c r="E36" s="369"/>
+      <c r="F36" s="369"/>
+      <c r="G36" s="369"/>
+      <c r="H36" s="369"/>
+      <c r="I36" s="369"/>
+      <c r="J36" s="369"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="129"/>
@@ -13529,24 +13529,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="289"/>
       <c r="C38" s="125"/>
-      <c r="D38" s="368" t="s">
+      <c r="D38" s="370" t="s">
         <v>6</v>
       </c>
-      <c r="E38" s="368"/>
-      <c r="F38" s="368"/>
-      <c r="G38" s="368"/>
-      <c r="H38" s="368"/>
-      <c r="I38" s="368"/>
-      <c r="J38" s="368"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
+      <c r="G38" s="370"/>
+      <c r="H38" s="370"/>
+      <c r="I38" s="370"/>
+      <c r="J38" s="370"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="368"/>
-      <c r="E39" s="368"/>
-      <c r="F39" s="368"/>
-      <c r="G39" s="368"/>
-      <c r="H39" s="368"/>
-      <c r="I39" s="368"/>
-      <c r="J39" s="368"/>
+      <c r="D39" s="370"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
+      <c r="G39" s="370"/>
+      <c r="H39" s="370"/>
+      <c r="I39" s="370"/>
+      <c r="J39" s="370"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="129"/>
@@ -13564,15 +13564,15 @@
         <v>7</v>
       </c>
       <c r="C41" s="125"/>
-      <c r="D41" s="382" t="s">
+      <c r="D41" s="367" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="382"/>
-      <c r="F41" s="382"/>
-      <c r="G41" s="382"/>
-      <c r="H41" s="382"/>
-      <c r="I41" s="382"/>
-      <c r="J41" s="382"/>
+      <c r="E41" s="367"/>
+      <c r="F41" s="367"/>
+      <c r="G41" s="367"/>
+      <c r="H41" s="367"/>
+      <c r="I41" s="367"/>
+      <c r="J41" s="367"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="125"/>
@@ -13586,30 +13586,30 @@
       <c r="J42" s="293"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="383" t="s">
+      <c r="B43" s="368" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="115"/>
-      <c r="D43" s="381" t="s">
+      <c r="D43" s="369" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="381"/>
-      <c r="F43" s="381"/>
-      <c r="G43" s="381"/>
-      <c r="H43" s="381"/>
-      <c r="I43" s="381"/>
-      <c r="J43" s="381"/>
+      <c r="E43" s="369"/>
+      <c r="F43" s="369"/>
+      <c r="G43" s="369"/>
+      <c r="H43" s="369"/>
+      <c r="I43" s="369"/>
+      <c r="J43" s="369"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="383"/>
+      <c r="B44" s="368"/>
       <c r="C44" s="115"/>
-      <c r="D44" s="381"/>
-      <c r="E44" s="381"/>
-      <c r="F44" s="381"/>
-      <c r="G44" s="381"/>
-      <c r="H44" s="381"/>
-      <c r="I44" s="381"/>
-      <c r="J44" s="381"/>
+      <c r="D44" s="369"/>
+      <c r="E44" s="369"/>
+      <c r="F44" s="369"/>
+      <c r="G44" s="369"/>
+      <c r="H44" s="369"/>
+      <c r="I44" s="369"/>
+      <c r="J44" s="369"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="124"/>
@@ -13621,17 +13621,17 @@
       <c r="J45" s="126"/>
     </row>
     <row r="46" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="381" t="s">
+      <c r="B46" s="369" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="381"/>
-      <c r="D46" s="381"/>
-      <c r="E46" s="381"/>
-      <c r="F46" s="381"/>
-      <c r="G46" s="381"/>
-      <c r="H46" s="381"/>
-      <c r="I46" s="381"/>
-      <c r="J46" s="381"/>
+      <c r="C46" s="369"/>
+      <c r="D46" s="369"/>
+      <c r="E46" s="369"/>
+      <c r="F46" s="369"/>
+      <c r="G46" s="369"/>
+      <c r="H46" s="369"/>
+      <c r="I46" s="369"/>
+      <c r="J46" s="369"/>
       <c r="K46" s="119"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -13666,17 +13666,17 @@
       <c r="J49" s="124"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="381" t="s">
+      <c r="B50" s="369" t="s">
         <v>13</v>
       </c>
-      <c r="C50" s="381"/>
-      <c r="D50" s="381"/>
-      <c r="E50" s="381"/>
-      <c r="F50" s="381"/>
-      <c r="G50" s="381"/>
-      <c r="H50" s="381"/>
-      <c r="I50" s="381"/>
-      <c r="J50" s="381"/>
+      <c r="C50" s="369"/>
+      <c r="D50" s="369"/>
+      <c r="E50" s="369"/>
+      <c r="F50" s="369"/>
+      <c r="G50" s="369"/>
+      <c r="H50" s="369"/>
+      <c r="I50" s="369"/>
+      <c r="J50" s="369"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="126"/>
@@ -13689,7 +13689,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="16" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="17"/>
@@ -13710,7 +13710,7 @@
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="326"/>
       <c r="B54" s="326" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C54" s="201"/>
       <c r="D54" s="201"/>
@@ -13719,7 +13719,7 @@
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="326"/>
       <c r="B55" s="326" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C55" s="201"/>
       <c r="D55" s="201"/>
@@ -13728,7 +13728,7 @@
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="326"/>
       <c r="B56" s="326" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C56" s="201"/>
       <c r="D56" s="201"/>
@@ -13737,7 +13737,7 @@
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="326"/>
       <c r="B57" s="327" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C57" s="201"/>
       <c r="D57" s="201"/>
@@ -13774,11 +13774,6 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -13791,6 +13786,11 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Projekt!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Laufleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -13835,7 +13835,7 @@
         <v>139</v>
       </c>
       <c r="E2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F2" s="137"/>
     </row>
@@ -13967,7 +13967,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -13983,9 +13983,9 @@
     </row>
     <row r="18" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="75" t="s">
-        <v>199</v>
-      </c>
-      <c r="C18" s="361">
+        <v>197</v>
+      </c>
+      <c r="C18" s="360">
         <f>0.0057*(ReichwPHEV4/23)^3-0.0838*(ReichwPHEV4/23)^2+0.4261*(ReichwPHEV4/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -13995,9 +13995,9 @@
     </row>
     <row r="19" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19" s="362">
+        <v>206</v>
+      </c>
+      <c r="C19" s="361">
         <f>Verbrauch4/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -14009,9 +14009,9 @@
     </row>
     <row r="20" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="75" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" s="363">
+        <v>207</v>
+      </c>
+      <c r="C20" s="362">
         <f>VerbEl_WLTP4/C18</f>
         <v>0</v>
       </c>
@@ -14023,9 +14023,9 @@
     </row>
     <row r="21" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="209" t="s">
-        <v>201</v>
-      </c>
-      <c r="C21" s="364">
+        <v>199</v>
+      </c>
+      <c r="C21" s="363">
         <f>0.0021*(ReichwPHEV4/23)^3-0.0358*(ReichwPHEV4/23)^2+0.2607*(ReichwPHEV4/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -14034,13 +14034,13 @@
       <c r="F21" s="203"/>
     </row>
     <row r="22" spans="1:6" s="201" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="428" t="s">
+      <c r="A22" s="427" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="427" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="365">
+      <c r="B22" s="426" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="364">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -14051,9 +14051,9 @@
       <c r="F22" s="203"/>
     </row>
     <row r="23" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="428"/>
-      <c r="B23" s="410"/>
-      <c r="C23" s="365">
+      <c r="A23" s="427"/>
+      <c r="B23" s="409"/>
+      <c r="C23" s="364">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -14094,7 +14094,7 @@
       <c r="B28" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="358">
+      <c r="C28" s="357">
         <f>IF(Antriebsart4="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie4,EnKostList,6,FALSE),0)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4,Verbrauch4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -14108,7 +14108,7 @@
       <c r="B29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="348">
+      <c r="C29" s="347">
         <f>IF(Antriebsart4="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbElPHEV4,VerbEl_WLTP4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -14122,7 +14122,7 @@
       <c r="B30" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="349">
+      <c r="C30" s="348">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -14154,7 +14154,7 @@
       <c r="B33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="358">
+      <c r="C33" s="357">
         <f>IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4*VLOOKUP(Energie4,CO2List,2,FALSE)/100,CO2_4)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -14168,7 +14168,7 @@
       <c r="B34" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="348">
+      <c r="C34" s="347">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -14182,7 +14182,7 @@
       <c r="B35" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="357">
+      <c r="C35" s="356">
         <f>IF(Energie4="Strom",0,NOX_4*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -14196,7 +14196,7 @@
       <c r="B36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="357">
+      <c r="C36" s="356">
         <f>IF(Energie4="Strom",0,Partikel4*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -14210,7 +14210,7 @@
       <c r="B37" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="349">
+      <c r="C37" s="348">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -14242,7 +14242,7 @@
       <c r="B40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="358">
+      <c r="C40" s="357">
         <f ca="1">IFERROR(IF(Antriebsart4="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP4/100*Fahrleistung/1000000,IF(Antriebsart4="Verbrenner",VLOOKUP(Energie4,CO2List,3,FALSE)*Verbrauch4/100*Fahrleistung/1000000,VLOOKUP(Energie4,CO2List,3,FALSE)*VerbPHEV4/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV4/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -14256,7 +14256,7 @@
       <c r="B41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="348">
+      <c r="C41" s="347">
         <f ca="1">C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -14299,13 +14299,13 @@
       <c r="F45" s="137"/>
     </row>
     <row r="46" spans="1:6" s="70" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="426" t="s">
+      <c r="A46" s="425" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="424" t="s">
+      <c r="B46" s="423" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="350">
+      <c r="C46" s="349">
         <f>IF(OR(Antriebsart4="Vollelektrisch (BEV)",Antriebsart4="Plug-In-Hybrid (PHEV)"),Batterie4*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -14316,9 +14316,9 @@
       <c r="F46" s="137"/>
     </row>
     <row r="47" spans="1:6" s="70" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="426"/>
-      <c r="B47" s="425"/>
-      <c r="C47" s="350" t="e">
+      <c r="A47" s="425"/>
+      <c r="B47" s="424"/>
+      <c r="C47" s="349" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -14332,7 +14332,7 @@
       <c r="B48" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="348" t="e">
+      <c r="C48" s="347" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -14369,7 +14369,7 @@
       <c r="B54" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="351">
+      <c r="C54" s="350">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis4,0),Gesamtpreis4*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl4,0))</f>
         <v>0</v>
       </c>
@@ -14384,7 +14384,7 @@
       <c r="B55" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="352">
+      <c r="C55" s="351">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -14398,7 +14398,7 @@
       <c r="B56" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="352">
+      <c r="C56" s="351">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -14411,7 +14411,7 @@
       <c r="B57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="352">
+      <c r="C57" s="351">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -14424,7 +14424,7 @@
       <c r="B58" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C58" s="352">
+      <c r="C58" s="351">
         <f ca="1">C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -14437,7 +14437,7 @@
       <c r="B59" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="353" t="e">
+      <c r="C59" s="352" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
@@ -14450,7 +14450,7 @@
       <c r="B60" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="354" t="e">
+      <c r="C60" s="353" t="e">
         <f ca="1">SUM(C54:C59)</f>
         <v>#DIV/0!</v>
       </c>
@@ -14472,7 +14472,7 @@
       <c r="B62" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="C62" s="355" t="e">
+      <c r="C62" s="354" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -14484,7 +14484,7 @@
       <c r="B63" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="356">
+      <c r="C63" s="355">
         <f ca="1">C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -14542,7 +14542,7 @@
         <v>140</v>
       </c>
       <c r="E2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F2" s="137"/>
     </row>
@@ -14677,7 +14677,7 @@
     </row>
     <row r="16" spans="2:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -14694,9 +14694,9 @@
     </row>
     <row r="18" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="75" t="s">
-        <v>199</v>
-      </c>
-      <c r="C18" s="361">
+        <v>197</v>
+      </c>
+      <c r="C18" s="360">
         <f>0.0057*(ReichwPHEV5/23)^3-0.0838*(ReichwPHEV5/23)^2+0.4261*(ReichwPHEV5/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -14706,9 +14706,9 @@
     </row>
     <row r="19" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19" s="362">
+        <v>206</v>
+      </c>
+      <c r="C19" s="361">
         <f>Verbrauch5/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -14720,9 +14720,9 @@
     </row>
     <row r="20" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="75" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" s="363">
+        <v>207</v>
+      </c>
+      <c r="C20" s="362">
         <f>VerbEl_WLTP5/C18</f>
         <v>0</v>
       </c>
@@ -14734,9 +14734,9 @@
     </row>
     <row r="21" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="209" t="s">
-        <v>201</v>
-      </c>
-      <c r="C21" s="364">
+        <v>199</v>
+      </c>
+      <c r="C21" s="363">
         <f>0.0021*(ReichwPHEV5/23)^3-0.0358*(ReichwPHEV5/23)^2+0.2607*(ReichwPHEV5/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -14745,13 +14745,13 @@
       <c r="F21" s="203"/>
     </row>
     <row r="22" spans="1:6" s="201" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="428" t="s">
+      <c r="A22" s="427" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="427" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="365">
+      <c r="B22" s="426" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="364">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -14762,9 +14762,9 @@
       <c r="F22" s="203"/>
     </row>
     <row r="23" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="428"/>
-      <c r="B23" s="410"/>
-      <c r="C23" s="365">
+      <c r="A23" s="427"/>
+      <c r="B23" s="409"/>
+      <c r="C23" s="364">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -14805,7 +14805,7 @@
       <c r="B28" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="358">
+      <c r="C28" s="357">
         <f>IF(Antriebsart5="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie5,EnKostList,6,FALSE),0)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5,Verbrauch5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -14819,7 +14819,7 @@
       <c r="B29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="358">
+      <c r="C29" s="357">
         <f>IF(Antriebsart5="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbElPHEV5,VerbEl_WLTP5)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -14833,7 +14833,7 @@
       <c r="B30" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="359">
+      <c r="C30" s="358">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -14866,7 +14866,7 @@
       <c r="B33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="358">
+      <c r="C33" s="357">
         <f>IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5*VLOOKUP(Energie5,CO2List,2,FALSE)/100,CO2_5)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -14880,7 +14880,7 @@
       <c r="B34" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="358">
+      <c r="C34" s="357">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -14894,7 +14894,7 @@
       <c r="B35" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="360">
+      <c r="C35" s="359">
         <f>IF(Energie5="Strom",0,NOX_5*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -14908,7 +14908,7 @@
       <c r="B36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="360">
+      <c r="C36" s="359">
         <f>IF(Energie5="Strom",0,Partikel5*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -14922,7 +14922,7 @@
       <c r="B37" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="359">
+      <c r="C37" s="358">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -14955,7 +14955,7 @@
       <c r="B40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="358">
+      <c r="C40" s="357">
         <f ca="1">IFERROR(IF(Antriebsart5="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP5/100*Fahrleistung/1000000,IF(Antriebsart5="Verbrenner",VLOOKUP(Energie5,CO2List,3,FALSE)*Verbrauch5/100*Fahrleistung/1000000,VLOOKUP(Energie5,CO2List,3,FALSE)*VerbPHEV5/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV5/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -14969,7 +14969,7 @@
       <c r="B41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="348">
+      <c r="C41" s="347">
         <f ca="1">C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -15012,13 +15012,13 @@
       <c r="F45" s="137"/>
     </row>
     <row r="46" spans="1:6" s="70" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="426" t="s">
+      <c r="A46" s="425" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="424" t="s">
+      <c r="B46" s="423" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="350">
+      <c r="C46" s="349">
         <f>IF(OR(Antriebsart5="Vollelektrisch (BEV)",Antriebsart5="Plug-In-Hybrid (PHEV)"),Batterie5*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -15029,9 +15029,9 @@
       <c r="F46" s="137"/>
     </row>
     <row r="47" spans="1:6" s="70" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="426"/>
-      <c r="B47" s="425"/>
-      <c r="C47" s="350" t="e">
+      <c r="A47" s="425"/>
+      <c r="B47" s="424"/>
+      <c r="C47" s="349" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -15045,7 +15045,7 @@
       <c r="B48" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="348" t="e">
+      <c r="C48" s="347" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -15082,7 +15082,7 @@
       <c r="B54" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="351">
+      <c r="C54" s="350">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis5,0),Gesamtpreis5*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl5,0))</f>
         <v>0</v>
       </c>
@@ -15097,7 +15097,7 @@
       <c r="B55" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="352">
+      <c r="C55" s="351">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -15111,7 +15111,7 @@
       <c r="B56" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="352">
+      <c r="C56" s="351">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15124,7 +15124,7 @@
       <c r="B57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="352">
+      <c r="C57" s="351">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15137,7 +15137,7 @@
       <c r="B58" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C58" s="352">
+      <c r="C58" s="351">
         <f ca="1">C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15150,7 +15150,7 @@
       <c r="B59" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="353" t="e">
+      <c r="C59" s="352" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
@@ -15163,7 +15163,7 @@
       <c r="B60" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="354" t="e">
+      <c r="C60" s="353" t="e">
         <f ca="1">SUM(C54:C59)</f>
         <v>#DIV/0!</v>
       </c>
@@ -15185,7 +15185,7 @@
       <c r="B62" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="C62" s="355" t="e">
+      <c r="C62" s="354" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -15197,7 +15197,7 @@
       <c r="B63" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="356">
+      <c r="C63" s="355">
         <f ca="1">C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15257,7 +15257,7 @@
         <v>141</v>
       </c>
       <c r="G2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -15355,14 +15355,14 @@
       <c r="B15" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="429" t="s">
-        <v>220</v>
-      </c>
-      <c r="D15" s="429"/>
-      <c r="E15" s="430" t="s">
+      <c r="C15" s="428" t="s">
+        <v>217</v>
+      </c>
+      <c r="D15" s="428"/>
+      <c r="E15" s="429" t="s">
         <v>148</v>
       </c>
-      <c r="F15" s="430"/>
+      <c r="F15" s="429"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="69"/>
@@ -15424,7 +15424,7 @@
     </row>
     <row r="20" spans="1:31" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="103" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D20" s="118"/>
       <c r="E20" s="10"/>
@@ -15440,13 +15440,13 @@
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B24" s="69"/>
       <c r="H24" s="147" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="I24" s="147"/>
       <c r="J24" s="147"/>
       <c r="K24" s="147"/>
       <c r="M24" s="151" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="N24" s="151"/>
       <c r="O24" s="151"/>
@@ -15558,7 +15558,7 @@
       </c>
     </row>
     <row r="27" spans="1:31" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A27" s="431" t="s">
+      <c r="A27" s="430" t="s">
         <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -15649,7 +15649,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A28" s="426"/>
+      <c r="A28" s="425"/>
       <c r="B28" s="1" t="s">
         <v>46</v>
       </c>
@@ -15760,7 +15760,7 @@
       </c>
     </row>
     <row r="29" spans="1:31" ht="16.2" x14ac:dyDescent="0.35">
-      <c r="A29" s="426"/>
+      <c r="A29" s="425"/>
       <c r="B29" s="1" t="s">
         <v>105</v>
       </c>
@@ -15838,7 +15838,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -15849,7 +15849,7 @@
         <v>162</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -15860,7 +15860,7 @@
         <v>162</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -15877,7 +15877,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -16005,12 +16005,12 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -16034,25 +16034,25 @@
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="281" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="281" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="281" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16063,12 +16063,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="331" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="I45" s="118"/>
     </row>
@@ -16078,31 +16078,31 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
@@ -16110,767 +16110,767 @@
         <v>26</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B128" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
@@ -16878,7 +16878,7 @@
         <v>164</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
@@ -16886,7 +16886,7 @@
         <v>165</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
@@ -16894,7 +16894,7 @@
         <v>167</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
@@ -16902,7 +16902,7 @@
         <v>169</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
@@ -16910,159 +16910,159 @@
         <v>170</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B155" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B156" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B157" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B163" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B164" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -17097,32 +17097,32 @@
       </c>
       <c r="C2" s="144"/>
       <c r="E2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="342" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C4" s="342" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="344" t="s">
+      <c r="C5" s="343" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="6" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="342" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C6" s="342" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="7" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="344" t="s">
+      <c r="C7" s="343" t="s">
         <v>177</v>
       </c>
     </row>
@@ -17135,74 +17135,74 @@
       </c>
     </row>
     <row r="9" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="344" t="s">
-        <v>463</v>
+      <c r="C9" s="343" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="10" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="342" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C10" s="335" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="344" t="s">
+      <c r="C11" s="343" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="12" spans="2:5" s="342" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="345" t="s">
+      <c r="B12" s="344" t="s">
         <v>181</v>
       </c>
       <c r="C12" s="335" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="13" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="335"/>
-      <c r="C13" s="344" t="s">
+      <c r="C13" s="343" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="14" spans="2:5" s="342" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="B14" s="346" t="s">
-        <v>497</v>
+      <c r="B14" s="345" t="s">
+        <v>511</v>
       </c>
       <c r="C14" s="342" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" s="342" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C15" s="431" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="345" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" s="342" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="334" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" s="342" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="346" t="s">
-        <v>503</v>
-      </c>
       <c r="C16" s="342" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" s="342" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" s="342" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="C17" s="343" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="103" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C18" s="103" t="s">
-        <v>187</v>
+        <v>512</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="334" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D19" s="334"/>
       <c r="E19" s="334"/>
@@ -17216,64 +17216,64 @@
         <v>103</v>
       </c>
       <c r="C20" s="342" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="2:9" s="342" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="344" t="s">
+      <c r="C21" s="343" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="22" spans="2:9" s="342" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="342" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C22" s="342" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
     </row>
     <row r="23" spans="2:9" s="342" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="344" t="s">
-        <v>202</v>
+      <c r="C23" s="343" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="2:9" s="342" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="342" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C24" s="342" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="2:9" s="342" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="344" t="s">
-        <v>207</v>
+      <c r="C25" s="343" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="2:9" s="342" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="342" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="342" t="s">
         <v>185</v>
       </c>
-      <c r="C26" s="342" t="s">
-        <v>186</v>
-      </c>
     </row>
     <row r="27" spans="2:9" s="342" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="344" t="s">
-        <v>471</v>
+      <c r="C27" s="343" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="2:9" s="342" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="342" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C28" s="342" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="2:9" s="342" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="334" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="2:9" s="342" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -17329,7 +17329,7 @@
         <v>14</v>
       </c>
       <c r="I2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -17347,50 +17347,50 @@
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="388"/>
-      <c r="D6" s="389"/>
-      <c r="E6" s="389"/>
-      <c r="F6" s="389"/>
-      <c r="G6" s="389"/>
-      <c r="H6" s="390"/>
+      <c r="C6" s="387"/>
+      <c r="D6" s="388"/>
+      <c r="E6" s="388"/>
+      <c r="F6" s="388"/>
+      <c r="G6" s="388"/>
+      <c r="H6" s="389"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C7" s="391"/>
-      <c r="D7" s="392"/>
-      <c r="E7" s="392"/>
-      <c r="F7" s="392"/>
-      <c r="G7" s="392"/>
-      <c r="H7" s="393"/>
+      <c r="C7" s="390"/>
+      <c r="D7" s="391"/>
+      <c r="E7" s="391"/>
+      <c r="F7" s="391"/>
+      <c r="G7" s="391"/>
+      <c r="H7" s="392"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="394"/>
-      <c r="D8" s="395"/>
-      <c r="E8" s="395"/>
-      <c r="F8" s="395"/>
-      <c r="G8" s="395"/>
-      <c r="H8" s="396"/>
+      <c r="C8" s="393"/>
+      <c r="D8" s="394"/>
+      <c r="E8" s="394"/>
+      <c r="F8" s="394"/>
+      <c r="G8" s="394"/>
+      <c r="H8" s="395"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="397"/>
-      <c r="D9" s="398"/>
-      <c r="E9" s="398"/>
-      <c r="F9" s="398"/>
-      <c r="G9" s="398"/>
-      <c r="H9" s="399"/>
+      <c r="C9" s="396"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
+      <c r="G9" s="397"/>
+      <c r="H9" s="398"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="397"/>
-      <c r="D10" s="398"/>
-      <c r="E10" s="398"/>
-      <c r="F10" s="398"/>
-      <c r="G10" s="398"/>
-      <c r="H10" s="399"/>
+      <c r="C10" s="396"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
+      <c r="G10" s="397"/>
+      <c r="H10" s="398"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -17418,8 +17418,8 @@
       <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="385"/>
-      <c r="D13" s="386"/>
+      <c r="C13" s="384"/>
+      <c r="D13" s="385"/>
       <c r="E13" s="57"/>
       <c r="F13" s="57"/>
       <c r="G13" s="57"/>
@@ -17490,14 +17490,14 @@
       <c r="A21" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="387" t="s">
+      <c r="B21" s="386" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="384"/>
-      <c r="D21" s="384"/>
+      <c r="C21" s="383"/>
+      <c r="D21" s="383"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="387"/>
+      <c r="B22" s="386"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B23" s="192"/>
@@ -17507,14 +17507,14 @@
         <v>9</v>
       </c>
       <c r="B24" s="192" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C24" s="168"/>
       <c r="D24" s="194" t="s">
         <v>109</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F24" s="341">
         <f>Grunddaten!E35</f>
@@ -17724,7 +17724,7 @@
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
       <c r="K2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
@@ -17873,10 +17873,10 @@
       <c r="I10" s="155"/>
       <c r="J10" s="285"/>
       <c r="K10" s="283"/>
-      <c r="L10" s="412" t="s">
-        <v>217</v>
-      </c>
-      <c r="M10" s="412"/>
+      <c r="L10" s="411" t="s">
+        <v>214</v>
+      </c>
+      <c r="M10" s="411"/>
       <c r="N10" s="283"/>
       <c r="O10" s="179"/>
       <c r="P10" s="179"/>
@@ -17894,12 +17894,12 @@
       <c r="H11" s="156"/>
       <c r="I11" s="156"/>
       <c r="J11" s="285"/>
-      <c r="K11" s="414" t="s">
-        <v>218</v>
-      </c>
-      <c r="L11" s="414"/>
-      <c r="M11" s="414"/>
-      <c r="N11" s="414"/>
+      <c r="K11" s="413" t="s">
+        <v>215</v>
+      </c>
+      <c r="L11" s="413"/>
+      <c r="M11" s="413"/>
+      <c r="N11" s="413"/>
       <c r="O11" s="179"/>
       <c r="P11" s="179"/>
       <c r="Q11" s="179"/>
@@ -17916,12 +17916,12 @@
       <c r="H12" s="156"/>
       <c r="I12" s="156"/>
       <c r="J12" s="179"/>
-      <c r="K12" s="413" t="s">
-        <v>216</v>
-      </c>
-      <c r="L12" s="413"/>
-      <c r="M12" s="413"/>
-      <c r="N12" s="413"/>
+      <c r="K12" s="412" t="s">
+        <v>213</v>
+      </c>
+      <c r="L12" s="412"/>
+      <c r="M12" s="412"/>
+      <c r="N12" s="412"/>
       <c r="O12" s="179"/>
       <c r="P12" s="179"/>
       <c r="Q12" s="179"/>
@@ -17932,7 +17932,7 @@
         <f>IF(ISBLANK(FinArt), "Art der Beschaffung wählen in:", VLOOKUP(FinArt,FinArtList,3,FALSE))</f>
         <v>Art der Beschaffung wählen in:</v>
       </c>
-      <c r="D13" s="347" t="str">
+      <c r="D13" s="346" t="str">
         <f>IF(ISBLANK(FinArt), "Input_Projekt", VLOOKUP(FinArt,FinArtList,2,FALSE))</f>
         <v>Input_Projekt</v>
       </c>
@@ -17953,7 +17953,7 @@
     </row>
     <row r="14" spans="2:18" s="102" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C14" s="177" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D14" s="324" t="s">
         <v>51</v>
@@ -17964,7 +17964,7 @@
       <c r="H14" s="157"/>
       <c r="I14" s="157"/>
       <c r="J14" s="325" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="K14" s="283"/>
       <c r="L14" s="283"/>
@@ -17976,10 +17976,10 @@
       <c r="R14" s="179"/>
     </row>
     <row r="15" spans="2:18" s="102" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="411" t="s">
+      <c r="B15" s="410" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="409" t="s">
+      <c r="C15" s="408" t="s">
         <v>53</v>
       </c>
       <c r="D15" s="183" t="s">
@@ -18000,8 +18000,8 @@
       <c r="R15" s="179"/>
     </row>
     <row r="16" spans="2:18" s="102" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="411"/>
-      <c r="C16" s="410"/>
+      <c r="B16" s="410"/>
+      <c r="C16" s="409"/>
       <c r="D16" s="181" t="s">
         <v>55</v>
       </c>
@@ -18021,7 +18021,7 @@
       <c r="R16" s="179"/>
     </row>
     <row r="17" spans="2:18" s="102" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="411"/>
+      <c r="B17" s="410"/>
       <c r="C17" s="177" t="s">
         <v>56</v>
       </c>
@@ -18044,12 +18044,12 @@
       <c r="R17" s="179"/>
     </row>
     <row r="18" spans="2:18" s="102" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="411"/>
+      <c r="B18" s="410"/>
       <c r="C18" s="177" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D18" s="181" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E18" s="319"/>
       <c r="F18" s="155"/>
@@ -18070,12 +18070,12 @@
       <c r="R18" s="179"/>
     </row>
     <row r="19" spans="2:18" s="102" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="411"/>
+      <c r="B19" s="410"/>
       <c r="C19" s="177" t="s">
         <v>59</v>
       </c>
       <c r="D19" s="181" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E19" s="319"/>
       <c r="F19" s="155"/>
@@ -18093,9 +18093,9 @@
       <c r="R19" s="179"/>
     </row>
     <row r="20" spans="2:18" s="102" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="411"/>
+      <c r="B20" s="410"/>
       <c r="C20" s="177" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D20" s="181" t="s">
         <v>94</v>
@@ -18139,7 +18139,7 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D22" s="274" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E22" s="277">
         <f>IF(AND(OR(Energie1="nicht verfügbar",COUNTIF(EnList1,Energie1)&lt;&gt;1),Antriebsart1&lt;&gt;0),1,0)</f>
@@ -18172,7 +18172,7 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D23" s="274" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E23" s="277">
         <f>IF(OR(AND(COUNT(E15:E21)&lt;7,Antriebsart1="Plug-In-Hybrid (PHEV)"),AND(COUNT(E16,E21)&lt;2,Antriebsart1="Vollelektrisch (BEV)"),AND(COUNT(E15,E17:E19)&lt;4,Antriebsart1="Verbrenner")),1,0)</f>
@@ -18204,29 +18204,29 @@
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="2:18" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="406" t="s">
-        <v>511</v>
-      </c>
-      <c r="F24" s="407"/>
-      <c r="G24" s="407"/>
-      <c r="H24" s="407"/>
-      <c r="I24" s="408"/>
+      <c r="E24" s="405" t="s">
+        <v>506</v>
+      </c>
+      <c r="F24" s="406"/>
+      <c r="G24" s="406"/>
+      <c r="H24" s="406"/>
+      <c r="I24" s="407"/>
     </row>
     <row r="25" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E25" s="400" t="s">
-        <v>512</v>
-      </c>
-      <c r="F25" s="401"/>
-      <c r="G25" s="401"/>
-      <c r="H25" s="401"/>
-      <c r="I25" s="402"/>
+      <c r="E25" s="399" t="s">
+        <v>507</v>
+      </c>
+      <c r="F25" s="400"/>
+      <c r="G25" s="400"/>
+      <c r="H25" s="400"/>
+      <c r="I25" s="401"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="E26" s="403"/>
-      <c r="F26" s="404"/>
-      <c r="G26" s="404"/>
-      <c r="H26" s="404"/>
-      <c r="I26" s="405"/>
+      <c r="E26" s="402"/>
+      <c r="F26" s="403"/>
+      <c r="G26" s="403"/>
+      <c r="H26" s="403"/>
+      <c r="I26" s="404"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C28" s="1" t="s">
@@ -18598,7 +18598,7 @@
       <c r="G2" s="275"/>
       <c r="H2" s="20"/>
       <c r="J2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -18702,11 +18702,11 @@
       <c r="B11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="415" t="str">
+      <c r="C11" s="414" t="str">
         <f>IF(Datum=0,"",Datum)</f>
         <v/>
       </c>
-      <c r="D11" s="416"/>
+      <c r="D11" s="415"/>
       <c r="E11" s="82"/>
       <c r="F11" s="84"/>
       <c r="G11" s="84"/>
@@ -18913,7 +18913,7 @@
       <c r="Q20" s="213"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="417" t="s">
+      <c r="A21" s="416" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="29" t="s">
@@ -18952,7 +18952,7 @@
       <c r="Q21" s="213"/>
     </row>
     <row r="22" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="417"/>
+      <c r="A22" s="416"/>
       <c r="B22" s="29" t="s">
         <v>70</v>
       </c>
@@ -18990,7 +18990,7 @@
       <c r="Q22" s="213"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="417"/>
+      <c r="A23" s="416"/>
       <c r="B23" s="31" t="s">
         <v>71</v>
       </c>
@@ -19089,7 +19089,7 @@
         <v>74</v>
       </c>
       <c r="C26" s="69" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D26" s="278">
         <f ca="1">IF(AND(COUNTIF(D19:D23,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D19:D23,0)&gt;1,Antriebsart1&lt;&gt;0),1,0))</f>
@@ -19332,7 +19332,7 @@
       <c r="G2" s="275"/>
       <c r="H2" s="20"/>
       <c r="J2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -19436,11 +19436,11 @@
       <c r="B11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="415" t="str">
+      <c r="C11" s="414" t="str">
         <f>IF(Datum=0,"",Datum)</f>
         <v/>
       </c>
-      <c r="D11" s="416"/>
+      <c r="D11" s="415"/>
       <c r="E11" s="82"/>
       <c r="F11" s="84"/>
       <c r="G11" s="84"/>
@@ -19548,7 +19548,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="417" t="s">
+      <c r="A18" s="416" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="29" t="s">
@@ -19587,7 +19587,7 @@
       <c r="Q18" s="213"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="417"/>
+      <c r="A19" s="416"/>
       <c r="B19" s="29" t="s">
         <v>80</v>
       </c>
@@ -19624,7 +19624,7 @@
       <c r="Q19" s="213"/>
     </row>
     <row r="20" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="417"/>
+      <c r="A20" s="416"/>
       <c r="B20" s="29" t="s">
         <v>70</v>
       </c>
@@ -19662,7 +19662,7 @@
       <c r="Q20" s="213"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="417"/>
+      <c r="A21" s="416"/>
       <c r="B21" s="31" t="s">
         <v>71</v>
       </c>
@@ -19761,7 +19761,7 @@
         <v>74</v>
       </c>
       <c r="C24" s="69" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D24" s="278">
         <f ca="1">IF(AND(COUNTIF(D18:D21,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D18:D21,0)&gt;1,Antriebsart1="Verbrenner"),1,IF(AND(COUNTIF(D18:D21,0)&gt;2,Antriebsart1&lt;&gt;""),1,0)))</f>
@@ -19992,7 +19992,7 @@
       <c r="G2" s="216"/>
       <c r="H2" s="131"/>
       <c r="I2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -20051,8 +20051,8 @@
     </row>
     <row r="7" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="217"/>
-      <c r="B7" s="418" t="s">
-        <v>197</v>
+      <c r="B7" s="417" t="s">
+        <v>195</v>
       </c>
       <c r="C7" s="265" t="s">
         <v>42</v>
@@ -20072,9 +20072,9 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="217"/>
-      <c r="B8" s="419"/>
+      <c r="B8" s="418"/>
       <c r="C8" s="265" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D8" s="266">
         <v>130</v>
@@ -20091,7 +20091,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="217"/>
-      <c r="B9" s="420"/>
+      <c r="B9" s="419"/>
       <c r="C9" s="265" t="s">
         <v>89</v>
       </c>
@@ -20111,7 +20111,7 @@
     <row r="10" spans="1:9" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A10" s="217"/>
       <c r="B10" s="267" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C10" s="265" t="s">
         <v>90</v>
@@ -20121,7 +20121,7 @@
       </c>
       <c r="E10" s="337"/>
       <c r="F10" s="265" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="G10" s="219">
         <f t="shared" si="0"/>
@@ -20132,7 +20132,7 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="217"/>
       <c r="B11" s="267" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C11" s="265" t="s">
         <v>90</v>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="E11" s="337"/>
       <c r="F11" s="265" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="G11" s="219">
         <f t="shared" si="0"/>
@@ -20152,8 +20152,8 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="217"/>
-      <c r="B12" s="418" t="s">
-        <v>489</v>
+      <c r="B12" s="417" t="s">
+        <v>486</v>
       </c>
       <c r="C12" s="265" t="s">
         <v>91</v>
@@ -20173,7 +20173,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="217"/>
-      <c r="B13" s="420"/>
+      <c r="B13" s="419"/>
       <c r="C13" s="265" t="s">
         <v>93</v>
       </c>
@@ -20193,7 +20193,7 @@
     <row r="14" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A14" s="260"/>
       <c r="B14" s="269" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C14" s="270" t="s">
         <v>89</v>
@@ -20238,7 +20238,7 @@
       </c>
       <c r="C18" s="221"/>
       <c r="D18" s="222" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E18" s="222"/>
       <c r="F18" s="222"/>
@@ -20314,7 +20314,7 @@
         <v>99</v>
       </c>
       <c r="I23" s="313" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -20335,7 +20335,7 @@
         <v>0.46299999999999997</v>
       </c>
       <c r="H24" s="228" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I24" s="312"/>
     </row>
@@ -20378,7 +20378,7 @@
       <c r="I26" s="312"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="422"/>
+      <c r="A27" s="421"/>
       <c r="B27" s="247" t="s">
         <v>45</v>
       </c>
@@ -20395,12 +20395,12 @@
         <v>1.659</v>
       </c>
       <c r="H27" s="228" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="I27" s="312"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="422"/>
+      <c r="A28" s="421"/>
       <c r="B28" s="247" t="s">
         <v>46</v>
       </c>
@@ -20417,7 +20417,7 @@
         <v>1.784</v>
       </c>
       <c r="H28" s="228" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="I28" s="312"/>
     </row>
@@ -20439,7 +20439,7 @@
         <v>1.2</v>
       </c>
       <c r="H29" s="228" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="I29" s="312"/>
     </row>
@@ -20480,13 +20480,13 @@
     </row>
     <row r="33" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="222"/>
-      <c r="B33" s="423" t="s">
-        <v>483</v>
-      </c>
-      <c r="C33" s="423"/>
-      <c r="D33" s="423"/>
-      <c r="E33" s="423"/>
-      <c r="F33" s="423"/>
+      <c r="B33" s="422" t="s">
+        <v>480</v>
+      </c>
+      <c r="C33" s="422"/>
+      <c r="D33" s="422"/>
+      <c r="E33" s="422"/>
+      <c r="F33" s="422"/>
       <c r="G33" s="246" t="s">
         <v>98</v>
       </c>
@@ -20525,7 +20525,7 @@
         <v>500</v>
       </c>
       <c r="H35" s="228" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="I35" s="312"/>
     </row>
@@ -20558,14 +20558,14 @@
         <v>0.02</v>
       </c>
       <c r="H37" s="228" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="I37" s="312"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="222"/>
       <c r="B38" s="201" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C38" s="201"/>
       <c r="D38" s="258">
@@ -20580,7 +20580,7 @@
         <v>0.15</v>
       </c>
       <c r="H38" s="228" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="I38" s="312"/>
     </row>
@@ -20609,7 +20609,7 @@
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="294"/>
       <c r="B41" s="298" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C41" s="299"/>
       <c r="D41" s="299"/>
@@ -20621,10 +20621,10 @@
     </row>
     <row r="42" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A42" s="294"/>
-      <c r="B42" s="421" t="s">
+      <c r="B42" s="420" t="s">
         <v>158</v>
       </c>
-      <c r="C42" s="421"/>
+      <c r="C42" s="420"/>
       <c r="D42" s="301">
         <v>84</v>
       </c>
@@ -20637,14 +20637,14 @@
         <v>84</v>
       </c>
       <c r="H42" s="228" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="I42" s="312"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="294"/>
       <c r="B43" s="304" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C43" s="305"/>
       <c r="D43" s="305"/>
@@ -20759,7 +20759,7 @@
         <v>112</v>
       </c>
       <c r="E2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="118"/>
@@ -20883,7 +20883,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -20898,9 +20898,9 @@
     </row>
     <row r="18" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="75" t="s">
-        <v>199</v>
-      </c>
-      <c r="C18" s="361">
+        <v>197</v>
+      </c>
+      <c r="C18" s="360">
         <f>0.0057*(ReichwPHEV1/23)^3-0.0838*(ReichwPHEV1/23)^2+0.4261*(ReichwPHEV1/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -20910,9 +20910,9 @@
     </row>
     <row r="19" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19" s="362">
+        <v>206</v>
+      </c>
+      <c r="C19" s="361">
         <f>Verbrauch1/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -20924,9 +20924,9 @@
     </row>
     <row r="20" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="75" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" s="363">
+        <v>207</v>
+      </c>
+      <c r="C20" s="362">
         <f>VerbEl_WLTP1/C18</f>
         <v>0</v>
       </c>
@@ -20938,9 +20938,9 @@
     </row>
     <row r="21" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="209" t="s">
-        <v>201</v>
-      </c>
-      <c r="C21" s="364">
+        <v>199</v>
+      </c>
+      <c r="C21" s="363">
         <f>0.0021*(ReichwPHEV1/23)^3-0.0358*(ReichwPHEV1/23)^2+0.2607*(ReichwPHEV1/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -20949,13 +20949,13 @@
       <c r="F21" s="203"/>
     </row>
     <row r="22" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="428" t="s">
+      <c r="A22" s="427" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="427" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="365">
+      <c r="B22" s="426" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="364">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -20966,9 +20966,9 @@
       <c r="F22" s="203"/>
     </row>
     <row r="23" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="428"/>
-      <c r="B23" s="410"/>
-      <c r="C23" s="365">
+      <c r="A23" s="427"/>
+      <c r="B23" s="409"/>
+      <c r="C23" s="364">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -21006,7 +21006,7 @@
       <c r="B28" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="348">
+      <c r="C28" s="347">
         <f>IF(Antriebsart1="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie1,EnKostList,6,FALSE),0)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1,Verbrauch1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -21019,7 +21019,7 @@
       <c r="B29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="348">
+      <c r="C29" s="347">
         <f>IF(Antriebsart1="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbElPHEV1,VerbEl_WLTP1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -21031,7 +21031,7 @@
       <c r="B30" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="349">
+      <c r="C30" s="348">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -21058,7 +21058,7 @@
       <c r="B33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="348">
+      <c r="C33" s="347">
         <f>IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1*VLOOKUP(Energie1,CO2List,2,FALSE)/100,CO2_1)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -21071,7 +21071,7 @@
       <c r="B34" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="348">
+      <c r="C34" s="347">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -21083,7 +21083,7 @@
       <c r="B35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="348">
+      <c r="C35" s="347">
         <f>IF(Energie1="Strom",0,NOX_1*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -21095,7 +21095,7 @@
       <c r="B36" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="348">
+      <c r="C36" s="347">
         <f>IF(Energie1="Strom",0,Partikel1*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -21107,7 +21107,7 @@
       <c r="B37" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="349">
+      <c r="C37" s="348">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -21132,7 +21132,7 @@
       <c r="B40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="348">
+      <c r="C40" s="347">
         <f ca="1">IFERROR(IF(Antriebsart1="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP1/100*Fahrleistung/1000000,IF(Antriebsart1="Verbrenner",VLOOKUP(Energie1,CO2List,3,FALSE)*Verbrauch1/100*Fahrleistung/1000000,VLOOKUP(Energie1,CO2List,3,FALSE)*VerbPHEV1/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV1/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -21145,7 +21145,7 @@
       <c r="B41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="348">
+      <c r="C41" s="347">
         <f ca="1">C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -21177,13 +21177,13 @@
       <c r="D45" s="64"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="426" t="s">
+      <c r="A46" s="425" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="424" t="s">
+      <c r="B46" s="423" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="350">
+      <c r="C46" s="349">
         <f>IF(OR(Antriebsart1="Vollelektrisch (BEV)",Antriebsart1="Plug-In-Hybrid (PHEV)"),Batterie1*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -21194,9 +21194,9 @@
       <c r="F46" s="119"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="426"/>
-      <c r="B47" s="425"/>
-      <c r="C47" s="366" t="e">
+      <c r="A47" s="425"/>
+      <c r="B47" s="424"/>
+      <c r="C47" s="365" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -21210,7 +21210,7 @@
       <c r="B48" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="358" t="e">
+      <c r="C48" s="357" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -21241,7 +21241,7 @@
       <c r="B54" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="351">
+      <c r="C54" s="350">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis1,0),Gesamtpreis1*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl1,0))</f>
         <v>0</v>
       </c>
@@ -21254,7 +21254,7 @@
       <c r="B55" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="352">
+      <c r="C55" s="351">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -21267,7 +21267,7 @@
       <c r="B56" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="352">
+      <c r="C56" s="351">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -21280,7 +21280,7 @@
       <c r="B57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="352">
+      <c r="C57" s="351">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -21293,7 +21293,7 @@
       <c r="B58" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C58" s="352">
+      <c r="C58" s="351">
         <f ca="1">C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -21306,7 +21306,7 @@
       <c r="B59" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="353" t="e">
+      <c r="C59" s="352" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
@@ -21319,7 +21319,7 @@
       <c r="B60" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="354" t="e">
+      <c r="C60" s="353" t="e">
         <f ca="1">SUM(C54:C59)</f>
         <v>#DIV/0!</v>
       </c>
@@ -21335,7 +21335,7 @@
       <c r="B62" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="C62" s="367" t="e">
+      <c r="C62" s="366" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -21347,7 +21347,7 @@
       <c r="B63" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="356">
+      <c r="C63" s="355">
         <f ca="1">C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -21404,7 +21404,7 @@
         <v>137</v>
       </c>
       <c r="E2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F2" s="137"/>
     </row>
@@ -21536,7 +21536,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -21552,9 +21552,9 @@
     </row>
     <row r="18" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="75" t="s">
-        <v>199</v>
-      </c>
-      <c r="C18" s="361">
+        <v>197</v>
+      </c>
+      <c r="C18" s="360">
         <f>0.0057*(ReichwPHEV2/23)^3-0.0838*(ReichwPHEV2/23)^2+0.4261*(ReichwPHEV2/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -21564,9 +21564,9 @@
     </row>
     <row r="19" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19" s="362">
+        <v>206</v>
+      </c>
+      <c r="C19" s="361">
         <f>Verbrauch2/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -21578,9 +21578,9 @@
     </row>
     <row r="20" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="75" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" s="363">
+        <v>207</v>
+      </c>
+      <c r="C20" s="362">
         <f>VerbEl_WLTP2/C18</f>
         <v>0</v>
       </c>
@@ -21592,9 +21592,9 @@
     </row>
     <row r="21" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="209" t="s">
-        <v>201</v>
-      </c>
-      <c r="C21" s="364">
+        <v>199</v>
+      </c>
+      <c r="C21" s="363">
         <f>0.0021*(ReichwPHEV2/23)^3-0.0358*(ReichwPHEV2/23)^2+0.2607*(ReichwPHEV2/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -21603,13 +21603,13 @@
       <c r="F21" s="203"/>
     </row>
     <row r="22" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="428" t="s">
+      <c r="A22" s="427" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="427" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="365">
+      <c r="B22" s="426" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="364">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -21620,9 +21620,9 @@
       <c r="F22" s="203"/>
     </row>
     <row r="23" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="428"/>
-      <c r="B23" s="410"/>
-      <c r="C23" s="365">
+      <c r="A23" s="427"/>
+      <c r="B23" s="409"/>
+      <c r="C23" s="364">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -21663,7 +21663,7 @@
       <c r="B28" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="348">
+      <c r="C28" s="347">
         <f>IF(Antriebsart2="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie2,EnKostList,6,FALSE),0)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2,Verbrauch2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -21677,7 +21677,7 @@
       <c r="B29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="348">
+      <c r="C29" s="347">
         <f>IF(Antriebsart2="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbElPHEV2,VerbEl_WLTP2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -21691,7 +21691,7 @@
       <c r="B30" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="349">
+      <c r="C30" s="348">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -21723,7 +21723,7 @@
       <c r="B33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="348">
+      <c r="C33" s="347">
         <f>IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2*VLOOKUP(Energie2,CO2List,2,FALSE)/100,CO2_2)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -21737,7 +21737,7 @@
       <c r="B34" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="348">
+      <c r="C34" s="347">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -21751,7 +21751,7 @@
       <c r="B35" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="357">
+      <c r="C35" s="356">
         <f>IF(Energie2="Strom",0,NOX_2*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -21765,7 +21765,7 @@
       <c r="B36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="357">
+      <c r="C36" s="356">
         <f>IF(Energie2="Strom",0,Partikel2*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -21779,7 +21779,7 @@
       <c r="B37" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="349">
+      <c r="C37" s="348">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -21811,7 +21811,7 @@
       <c r="B40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="348">
+      <c r="C40" s="347">
         <f ca="1">IFERROR(IF(Antriebsart2="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP2/100*Fahrleistung/1000000,IF(Antriebsart2="Verbrenner",VLOOKUP(Energie2,CO2List,3,FALSE)*Verbrauch2/100*Fahrleistung/1000000,VLOOKUP(Energie2,CO2List,3,FALSE)*VerbPHEV2/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV2/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -21825,7 +21825,7 @@
       <c r="B41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="348">
+      <c r="C41" s="347">
         <f ca="1">C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -21868,13 +21868,13 @@
       <c r="F45" s="137"/>
     </row>
     <row r="46" spans="1:6" s="70" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="426" t="s">
+      <c r="A46" s="425" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="424" t="s">
+      <c r="B46" s="423" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="350">
+      <c r="C46" s="349">
         <f>IF(OR(Antriebsart2="Vollelektrisch (BEV)",Antriebsart2="Plug-In-Hybrid (PHEV)"),Batterie2*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -21885,9 +21885,9 @@
       <c r="F46" s="137"/>
     </row>
     <row r="47" spans="1:6" s="70" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="426"/>
-      <c r="B47" s="425"/>
-      <c r="C47" s="350" t="e">
+      <c r="A47" s="425"/>
+      <c r="B47" s="424"/>
+      <c r="C47" s="349" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -21901,7 +21901,7 @@
       <c r="B48" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="348" t="e">
+      <c r="C48" s="347" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -21938,7 +21938,7 @@
       <c r="B54" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="351">
+      <c r="C54" s="350">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis2,0),Gesamtpreis2*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl2,0))</f>
         <v>0</v>
       </c>
@@ -21953,7 +21953,7 @@
       <c r="B55" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="352">
+      <c r="C55" s="351">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -21967,7 +21967,7 @@
       <c r="B56" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="352">
+      <c r="C56" s="351">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -21980,7 +21980,7 @@
       <c r="B57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="352">
+      <c r="C57" s="351">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -21993,7 +21993,7 @@
       <c r="B58" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C58" s="352">
+      <c r="C58" s="351">
         <f ca="1">C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -22006,7 +22006,7 @@
       <c r="B59" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="353" t="e">
+      <c r="C59" s="352" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
@@ -22019,7 +22019,7 @@
       <c r="B60" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="354" t="e">
+      <c r="C60" s="353" t="e">
         <f ca="1">SUM(C54:C59)</f>
         <v>#DIV/0!</v>
       </c>
@@ -22041,7 +22041,7 @@
       <c r="B62" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="C62" s="355" t="e">
+      <c r="C62" s="354" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -22053,7 +22053,7 @@
       <c r="B63" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="356">
+      <c r="C63" s="355">
         <f ca="1">C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -22111,7 +22111,7 @@
         <v>138</v>
       </c>
       <c r="E2" s="118" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F2" s="137"/>
     </row>
@@ -22243,7 +22243,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -22259,9 +22259,9 @@
     </row>
     <row r="18" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="75" t="s">
-        <v>199</v>
-      </c>
-      <c r="C18" s="361">
+        <v>197</v>
+      </c>
+      <c r="C18" s="360">
         <f>0.0057*(ReichwPHEV3/23)^3-0.0838*(ReichwPHEV3/23)^2+0.4261*(ReichwPHEV3/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -22271,9 +22271,9 @@
     </row>
     <row r="19" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19" s="362">
+        <v>206</v>
+      </c>
+      <c r="C19" s="361">
         <f>Verbrauch3/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -22285,9 +22285,9 @@
     </row>
     <row r="20" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="75" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" s="363">
+        <v>207</v>
+      </c>
+      <c r="C20" s="362">
         <f>VerbEl_WLTP3/C18</f>
         <v>0</v>
       </c>
@@ -22299,9 +22299,9 @@
     </row>
     <row r="21" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="209" t="s">
-        <v>201</v>
-      </c>
-      <c r="C21" s="364">
+        <v>199</v>
+      </c>
+      <c r="C21" s="363">
         <f>0.0021*(ReichwPHEV3/23)^3-0.0358*(ReichwPHEV3/23)^2+0.2607*(ReichwPHEV3/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -22310,13 +22310,13 @@
       <c r="F21" s="203"/>
     </row>
     <row r="22" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="428" t="s">
+      <c r="A22" s="427" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="427" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="365">
+      <c r="B22" s="426" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="364">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -22327,9 +22327,9 @@
       <c r="F22" s="203"/>
     </row>
     <row r="23" spans="1:6" s="201" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="428"/>
-      <c r="B23" s="410"/>
-      <c r="C23" s="365">
+      <c r="A23" s="427"/>
+      <c r="B23" s="409"/>
+      <c r="C23" s="364">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -22370,7 +22370,7 @@
       <c r="B28" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="348">
+      <c r="C28" s="347">
         <f>IF(Antriebsart3="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie3,EnKostList,6,FALSE),0)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3,Verbrauch3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -22384,7 +22384,7 @@
       <c r="B29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="348">
+      <c r="C29" s="347">
         <f>IF(Antriebsart3="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbElPHEV3,VerbEl_WLTP3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -22398,7 +22398,7 @@
       <c r="B30" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="349">
+      <c r="C30" s="348">
         <f>SUM(C28:C29)</f>
         <v>0</v>
       </c>
@@ -22430,7 +22430,7 @@
       <c r="B33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="348">
+      <c r="C33" s="347">
         <f>IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3*VLOOKUP(Energie3,CO2List,2,FALSE)/100,CO2_3)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -22444,7 +22444,7 @@
       <c r="B34" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="348">
+      <c r="C34" s="347">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -22458,7 +22458,7 @@
       <c r="B35" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="357">
+      <c r="C35" s="356">
         <f>IF(Energie3="Strom",0,NOX_3*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -22472,7 +22472,7 @@
       <c r="B36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="357">
+      <c r="C36" s="356">
         <f>IF(Energie3="Strom",0,Partikel3*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -22486,7 +22486,7 @@
       <c r="B37" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="349">
+      <c r="C37" s="348">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -22518,7 +22518,7 @@
       <c r="B40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="348">
+      <c r="C40" s="347">
         <f ca="1">IFERROR(IF(Antriebsart3="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP3/100*Fahrleistung/1000000,IF(Antriebsart3="Verbrenner",VLOOKUP(Energie3,CO2List,3,FALSE)*Verbrauch3/100*Fahrleistung/1000000,VLOOKUP(Energie3,CO2List,3,FALSE)*VerbPHEV3/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV3/100*Fahrleistung/1000000)),0)</f>
         <v>0</v>
       </c>
@@ -22532,7 +22532,7 @@
       <c r="B41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="348">
+      <c r="C41" s="347">
         <f ca="1">C40*Kost_THG</f>
         <v>0</v>
       </c>
@@ -22575,13 +22575,13 @@
       <c r="F45" s="137"/>
     </row>
     <row r="46" spans="1:6" s="70" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="426" t="s">
+      <c r="A46" s="425" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="424" t="s">
+      <c r="B46" s="423" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="350">
+      <c r="C46" s="349">
         <f>IF(OR(Antriebsart3="Vollelektrisch (BEV)",Antriebsart3="Plug-In-Hybrid (PHEV)"),Batterie3*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -22592,9 +22592,9 @@
       <c r="F46" s="145"/>
     </row>
     <row r="47" spans="1:6" s="70" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="426"/>
-      <c r="B47" s="425"/>
-      <c r="C47" s="350" t="e">
+      <c r="A47" s="425"/>
+      <c r="B47" s="424"/>
+      <c r="C47" s="349" t="e">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>#DIV/0!</v>
       </c>
@@ -22608,7 +22608,7 @@
       <c r="B48" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="348" t="e">
+      <c r="C48" s="347" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>#DIV/0!</v>
       </c>
@@ -22645,7 +22645,7 @@
       <c r="B54" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="351">
+      <c r="C54" s="350">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis3,0),Gesamtpreis3*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl3,0))</f>
         <v>0</v>
       </c>
@@ -22660,7 +22660,7 @@
       <c r="B55" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="352">
+      <c r="C55" s="351">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>0</v>
       </c>
@@ -22674,7 +22674,7 @@
       <c r="B56" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="352">
+      <c r="C56" s="351">
         <f>C30*Haltedauer</f>
         <v>0</v>
       </c>
@@ -22687,7 +22687,7 @@
       <c r="B57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="352">
+      <c r="C57" s="351">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -22700,7 +22700,7 @@
       <c r="B58" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C58" s="352">
+      <c r="C58" s="351">
         <f ca="1">C41*Haltedauer</f>
         <v>0</v>
       </c>
@@ -22713,7 +22713,7 @@
       <c r="B59" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="353" t="e">
+      <c r="C59" s="352" t="e">
         <f>C48*Haltedauer</f>
         <v>#DIV/0!</v>
       </c>
@@ -22726,7 +22726,7 @@
       <c r="B60" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="354" t="e">
+      <c r="C60" s="353" t="e">
         <f ca="1">SUM(C54:C59)</f>
         <v>#DIV/0!</v>
       </c>
@@ -22748,7 +22748,7 @@
       <c r="B62" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="C62" s="355" t="e">
+      <c r="C62" s="354" t="e">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>#DIV/0!</v>
       </c>
@@ -22760,7 +22760,7 @@
       <c r="B63" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="356">
+      <c r="C63" s="355">
         <f ca="1">C33*Haltedauer+C40*Haltedauer</f>
         <v>0</v>
       </c>
@@ -22793,9 +22793,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101009B43F9A2BF99C145A97E1F24240CACC5" ma:contentTypeVersion="3" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="ad7cb359a54e5cc452fc9ddca52c1c6e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0b6e3095-4fd5-4f76-ae54-62b873214d55" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a0e0858071e0fd1d5bbfdbf33b5c725" ns2:_="">
-    <xsd:import namespace="0b6e3095-4fd5-4f76-ae54-62b873214d55"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006A4EC2B1D245C948A7120CE5A36078F8" ma:contentTypeVersion="12" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="ded47abe6d3759cf0049106b5a3c7542">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e4dc333-02c0-4d6f-a03d-d04a548a7be7" xmlns:ns3="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="900ca3136c4d3a875f9ac343904324d4" ns2:_="" ns3:_="">
+    <xsd:import namespace="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <xsd:import namespace="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -22804,7 +22825,15 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -22812,7 +22841,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0b6e3095-4fd5-4f76-ae54-62b873214d55" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5e4dc333-02c0-4d6f-a03d-d04a548a7be7" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -22825,10 +22854,80 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7c880037-8306-4d34-9a7c-4fa698df1335" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="18" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="19" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Freigegeben für" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Freigegeben für - Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{80429792-8a2b-42f5-9b3c-1813633e58a8}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -22930,46 +23029,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A61372-8E32-4858-8148-26B097EA79D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A101028-5A28-43F4-AC06-8B329FE7CFE0}"/>
 </file>